--- a/20240403_Er_test/output/20240403_Er_test_element_pairs.xlsx
+++ b/20240403_Er_test/output/20240403_Er_test_element_pairs.xlsx
@@ -10,9 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ga" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ni" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-Co" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Co" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="In-In" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Er-In" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-In" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
@@ -671,11 +671,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.055</v>
+        <v>3.009</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy with atomic mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.055</v>
+        <v>3.009</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
@@ -813,11 +813,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.009</v>
+        <v>3.055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Full occupancy</t>
+          <t>Full occupancy with atomic mixing</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.009</v>
+        <v>3.055</v>
       </c>
       <c r="C4" t="inlineStr"/>
     </row>
